--- a/ig/mc-changes-1.0.1/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/ig/mc-changes-1.0.1/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-08T09:27:05+00:00</t>
+    <t>2023-06-08T09:38:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -354,7 +354,7 @@
     <t>as-data-trace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-data-trace}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace}
 </t>
   </si>
   <si>

--- a/ig/mc-changes-1.0.1/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/ig/mc-changes-1.0.1/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-08T09:38:17+00:00</t>
+    <t>2023-06-08T10:00:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
